--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128934517</v>
       </c>
       <c r="B2" t="n">
-        <v>96914</v>
+        <v>96918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +775,7 @@
         <v>128934524</v>
       </c>
       <c r="B3" t="n">
-        <v>96121</v>
+        <v>96125</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>128934521</v>
       </c>
       <c r="B5" t="n">
-        <v>75015</v>
+        <v>75019</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,17 +1056,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934526</v>
+        <v>128934527</v>
       </c>
       <c r="B6" t="n">
-        <v>95978</v>
+        <v>8439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2818</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>128934522</v>
       </c>
       <c r="B7" t="n">
-        <v>75143</v>
+        <v>75147</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,17 +1250,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128934527</v>
+        <v>128934526</v>
       </c>
       <c r="B8" t="n">
-        <v>8439</v>
+        <v>95982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
         <v>128934530</v>
       </c>
       <c r="B9" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1056,17 +1056,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934527</v>
+        <v>128934526</v>
       </c>
       <c r="B6" t="n">
-        <v>8439</v>
+        <v>95982</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1250,17 +1250,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128934526</v>
+        <v>128934527</v>
       </c>
       <c r="B8" t="n">
-        <v>95982</v>
+        <v>8439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128934517</v>
       </c>
       <c r="B2" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934524</v>
       </c>
       <c r="B3" t="n">
-        <v>96125</v>
+        <v>96132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>128934521</v>
       </c>
       <c r="B5" t="n">
-        <v>75019</v>
+        <v>75022</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
         <v>128934526</v>
       </c>
       <c r="B6" t="n">
-        <v>95982</v>
+        <v>95989</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>128934522</v>
       </c>
       <c r="B7" t="n">
-        <v>75147</v>
+        <v>75150</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
         <v>128934530</v>
       </c>
       <c r="B9" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934526</v>
+        <v>128934522</v>
       </c>
       <c r="B6" t="n">
-        <v>95997</v>
+        <v>75155</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552167</v>
+        <v>552339</v>
       </c>
       <c r="R6" t="n">
-        <v>6516407</v>
+        <v>6516255</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128934522</v>
+        <v>128934527</v>
       </c>
       <c r="B7" t="n">
-        <v>75155</v>
+        <v>8439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552339</v>
+        <v>552167</v>
       </c>
       <c r="R7" t="n">
-        <v>6516255</v>
+        <v>6516407</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128934527</v>
+        <v>128934526</v>
       </c>
       <c r="B8" t="n">
-        <v>8439</v>
+        <v>95997</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128934517</v>
       </c>
       <c r="B2" t="n">
-        <v>96933</v>
+        <v>96938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934524</v>
       </c>
       <c r="B3" t="n">
-        <v>96140</v>
+        <v>96145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934522</v>
+        <v>128934527</v>
       </c>
       <c r="B6" t="n">
-        <v>75155</v>
+        <v>8439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552339</v>
+        <v>552167</v>
       </c>
       <c r="R6" t="n">
-        <v>6516255</v>
+        <v>6516407</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128934527</v>
+        <v>128934526</v>
       </c>
       <c r="B7" t="n">
-        <v>8439</v>
+        <v>96002</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128934526</v>
+        <v>128934522</v>
       </c>
       <c r="B8" t="n">
-        <v>95997</v>
+        <v>75155</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552167</v>
+        <v>552339</v>
       </c>
       <c r="R8" t="n">
-        <v>6516407</v>
+        <v>6516255</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128934517</v>
       </c>
       <c r="B2" t="n">
-        <v>96938</v>
+        <v>96941</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934524</v>
       </c>
       <c r="B3" t="n">
-        <v>96145</v>
+        <v>96148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128934526</v>
       </c>
       <c r="B7" t="n">
-        <v>96002</v>
+        <v>96005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128934530</v>
       </c>
       <c r="B9" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128934526</v>
+        <v>128934522</v>
       </c>
       <c r="B7" t="n">
-        <v>96005</v>
+        <v>75155</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552167</v>
+        <v>552339</v>
       </c>
       <c r="R7" t="n">
-        <v>6516407</v>
+        <v>6516255</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128934522</v>
+        <v>128934526</v>
       </c>
       <c r="B8" t="n">
-        <v>75155</v>
+        <v>96005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552339</v>
+        <v>552167</v>
       </c>
       <c r="R8" t="n">
-        <v>6516255</v>
+        <v>6516407</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934527</v>
+        <v>128934526</v>
       </c>
       <c r="B6" t="n">
-        <v>8439</v>
+        <v>96005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128934526</v>
+        <v>128934527</v>
       </c>
       <c r="B8" t="n">
-        <v>96005</v>
+        <v>8439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128934517</v>
       </c>
       <c r="B2" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934524</v>
       </c>
       <c r="B3" t="n">
-        <v>96148</v>
+        <v>96158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128934521</v>
       </c>
       <c r="B5" t="n">
-        <v>75027</v>
+        <v>75029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128934526</v>
       </c>
       <c r="B6" t="n">
-        <v>96005</v>
+        <v>96015</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128934522</v>
       </c>
       <c r="B7" t="n">
-        <v>75155</v>
+        <v>75157</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128934530</v>
       </c>
       <c r="B9" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128934517</v>
       </c>
       <c r="B2" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934524</v>
       </c>
       <c r="B3" t="n">
-        <v>96158</v>
+        <v>96165</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934526</v>
+        <v>128934522</v>
       </c>
       <c r="B6" t="n">
-        <v>96015</v>
+        <v>75157</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552167</v>
+        <v>552339</v>
       </c>
       <c r="R6" t="n">
-        <v>6516407</v>
+        <v>6516255</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128934522</v>
+        <v>128934526</v>
       </c>
       <c r="B7" t="n">
-        <v>75157</v>
+        <v>96022</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552339</v>
+        <v>552167</v>
       </c>
       <c r="R7" t="n">
-        <v>6516255</v>
+        <v>6516407</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128934517</v>
       </c>
       <c r="B2" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934524</v>
       </c>
       <c r="B3" t="n">
-        <v>96165</v>
+        <v>96167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128934521</v>
       </c>
       <c r="B5" t="n">
-        <v>75029</v>
+        <v>75031</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128934522</v>
       </c>
       <c r="B6" t="n">
-        <v>75157</v>
+        <v>75159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128934526</v>
       </c>
       <c r="B7" t="n">
-        <v>96022</v>
+        <v>96024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128934530</v>
       </c>
       <c r="B9" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934522</v>
+        <v>128934527</v>
       </c>
       <c r="B6" t="n">
-        <v>75159</v>
+        <v>8439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552339</v>
+        <v>552167</v>
       </c>
       <c r="R6" t="n">
-        <v>6516255</v>
+        <v>6516407</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128934527</v>
+        <v>128934522</v>
       </c>
       <c r="B8" t="n">
-        <v>8439</v>
+        <v>75159</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552167</v>
+        <v>552339</v>
       </c>
       <c r="R8" t="n">
-        <v>6516407</v>
+        <v>6516255</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128934517</v>
       </c>
       <c r="B2" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934524</v>
       </c>
       <c r="B3" t="n">
-        <v>96167</v>
+        <v>96193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934527</v>
+        <v>128934522</v>
       </c>
       <c r="B6" t="n">
-        <v>8439</v>
+        <v>75159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552167</v>
+        <v>552339</v>
       </c>
       <c r="R6" t="n">
-        <v>6516407</v>
+        <v>6516255</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1163,7 +1163,7 @@
         <v>128934526</v>
       </c>
       <c r="B7" t="n">
-        <v>96024</v>
+        <v>96050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128934522</v>
+        <v>128934527</v>
       </c>
       <c r="B8" t="n">
-        <v>75159</v>
+        <v>8439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552339</v>
+        <v>552167</v>
       </c>
       <c r="R8" t="n">
-        <v>6516255</v>
+        <v>6516407</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128934517</v>
       </c>
       <c r="B2" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934524</v>
       </c>
       <c r="B3" t="n">
-        <v>96193</v>
+        <v>96194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934522</v>
+        <v>128934526</v>
       </c>
       <c r="B6" t="n">
-        <v>75159</v>
+        <v>96051</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552339</v>
+        <v>552167</v>
       </c>
       <c r="R6" t="n">
-        <v>6516255</v>
+        <v>6516407</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128934526</v>
+        <v>128934522</v>
       </c>
       <c r="B7" t="n">
-        <v>96050</v>
+        <v>75159</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552167</v>
+        <v>552339</v>
       </c>
       <c r="R7" t="n">
-        <v>6516407</v>
+        <v>6516255</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128934517</v>
       </c>
       <c r="B2" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934524</v>
       </c>
       <c r="B3" t="n">
-        <v>96194</v>
+        <v>96195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128934526</v>
       </c>
       <c r="B6" t="n">
-        <v>96051</v>
+        <v>96052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128934517</v>
       </c>
       <c r="B2" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934524</v>
       </c>
       <c r="B3" t="n">
-        <v>96195</v>
+        <v>96199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128934521</v>
       </c>
       <c r="B5" t="n">
-        <v>75031</v>
+        <v>75033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934526</v>
+        <v>128934522</v>
       </c>
       <c r="B6" t="n">
-        <v>96052</v>
+        <v>75161</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552167</v>
+        <v>552339</v>
       </c>
       <c r="R6" t="n">
-        <v>6516407</v>
+        <v>6516255</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128934522</v>
+        <v>128934526</v>
       </c>
       <c r="B7" t="n">
-        <v>75159</v>
+        <v>96056</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552339</v>
+        <v>552167</v>
       </c>
       <c r="R7" t="n">
-        <v>6516255</v>
+        <v>6516407</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1357,7 +1357,7 @@
         <v>128934530</v>
       </c>
       <c r="B9" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128934517</v>
       </c>
       <c r="B2" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934524</v>
       </c>
       <c r="B3" t="n">
-        <v>96199</v>
+        <v>96201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934522</v>
+        <v>128934527</v>
       </c>
       <c r="B6" t="n">
-        <v>75161</v>
+        <v>8439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552339</v>
+        <v>552167</v>
       </c>
       <c r="R6" t="n">
-        <v>6516255</v>
+        <v>6516407</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1163,7 +1163,7 @@
         <v>128934526</v>
       </c>
       <c r="B7" t="n">
-        <v>96056</v>
+        <v>96058</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128934527</v>
+        <v>128934522</v>
       </c>
       <c r="B8" t="n">
-        <v>8439</v>
+        <v>75161</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552167</v>
+        <v>552339</v>
       </c>
       <c r="R8" t="n">
-        <v>6516407</v>
+        <v>6516255</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1357,7 +1357,7 @@
         <v>128934530</v>
       </c>
       <c r="B9" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128934517</v>
       </c>
       <c r="B2" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934524</v>
       </c>
       <c r="B3" t="n">
-        <v>96201</v>
+        <v>96205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128934526</v>
       </c>
       <c r="B7" t="n">
-        <v>96058</v>
+        <v>96062</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128934517</v>
       </c>
       <c r="B2" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934524</v>
       </c>
       <c r="B3" t="n">
-        <v>96205</v>
+        <v>96213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128934526</v>
       </c>
       <c r="B7" t="n">
-        <v>96062</v>
+        <v>96070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -898,6 +898,15 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sydväst Stamfjärden, Ög</t>
@@ -948,6 +957,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1092,6 +1102,15 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sydväst Stamfjärden, Ög</t>
@@ -1142,6 +1161,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128934518</v>
       </c>
       <c r="B4" t="n">
-        <v>8439</v>
+        <v>8440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128934527</v>
       </c>
       <c r="B6" t="n">
-        <v>8439</v>
+        <v>8440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128934517</v>
+        <v>128934524</v>
       </c>
       <c r="B2" t="n">
-        <v>97006</v>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552390</v>
+        <v>552251</v>
       </c>
       <c r="R2" t="n">
-        <v>6516263</v>
+        <v>6516357</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128934524</v>
+        <v>128934517</v>
       </c>
       <c r="B3" t="n">
-        <v>96213</v>
+        <v>97394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>2590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552251</v>
+        <v>552390</v>
       </c>
       <c r="R3" t="n">
-        <v>6516357</v>
+        <v>6516263</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128934518</v>
+        <v>128934526</v>
       </c>
       <c r="B4" t="n">
-        <v>8440</v>
+        <v>96458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,43 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sydväst Stamfjärden, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552425</v>
+        <v>552167</v>
       </c>
       <c r="R4" t="n">
-        <v>6516246</v>
+        <v>6516407</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -957,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -976,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128934521</v>
+        <v>128934522</v>
       </c>
       <c r="B5" t="n">
-        <v>75033</v>
+        <v>75428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552434</v>
+        <v>552339</v>
       </c>
       <c r="R5" t="n">
-        <v>6516223</v>
+        <v>6516255</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1073,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934527</v>
+        <v>128934521</v>
       </c>
       <c r="B6" t="n">
-        <v>8440</v>
+        <v>75300</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,43 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>6428</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sydväst Stamfjärden, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552167</v>
+        <v>552434</v>
       </c>
       <c r="R6" t="n">
-        <v>6516407</v>
+        <v>6516223</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1161,7 +1142,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1180,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128934526</v>
+        <v>128934530</v>
       </c>
       <c r="B7" t="n">
-        <v>96070</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2818</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552167</v>
+        <v>552240</v>
       </c>
       <c r="R7" t="n">
-        <v>6516407</v>
+        <v>6516370</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1277,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128934522</v>
+        <v>128934518</v>
       </c>
       <c r="B8" t="n">
-        <v>75161</v>
+        <v>8444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,34 +1268,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sydväst Stamfjärden, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552339</v>
+        <v>552425</v>
       </c>
       <c r="R8" t="n">
-        <v>6516255</v>
+        <v>6516246</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1356,6 +1345,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1374,45 +1364,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934530</v>
+        <v>128934527</v>
       </c>
       <c r="B9" t="n">
-        <v>78801</v>
+        <v>8444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sydväst Stamfjärden, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552240</v>
+        <v>552167</v>
       </c>
       <c r="R9" t="n">
-        <v>6516370</v>
+        <v>6516407</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1453,6 +1452,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39827-2025 artfynd.xlsx
+++ b/artfynd/A 39827-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934524</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934517</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934526</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934522</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934521</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934530</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934518</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,8 +1508,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934527</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>